--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N105_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N105_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.05622494581414</v>
+        <v>2.121636553694798</v>
       </c>
       <c r="D2" t="n">
-        <v>12.59445180200965</v>
+        <v>2.046598417826568</v>
       </c>
       <c r="E2" t="n">
-        <v>13.30578548438424</v>
+        <v>2.16219014121244</v>
       </c>
       <c r="F2" t="n">
-        <v>12.50933283402449</v>
+        <v>2.032766585528979</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.06694556055416</v>
+        <v>4.398378653590052</v>
       </c>
       <c r="D3" t="n">
-        <v>27.1406007291284</v>
+        <v>4.410347618483366</v>
       </c>
       <c r="E3" t="n">
-        <v>13.30578548438424</v>
+        <v>2.16219014121244</v>
       </c>
       <c r="F3" t="n">
-        <v>12.50933283402449</v>
+        <v>2.032766585528979</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.78605228791898</v>
+        <v>4.677733496786835</v>
       </c>
       <c r="D4" t="n">
-        <v>29.19842580287028</v>
+        <v>4.744744192966421</v>
       </c>
       <c r="E4" t="n">
-        <v>13.30578548438424</v>
+        <v>2.16219014121244</v>
       </c>
       <c r="F4" t="n">
-        <v>12.50933283402449</v>
+        <v>2.032766585528979</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>1.851522449281035</v>
+        <v>0.3008723980081682</v>
       </c>
       <c r="D5" t="n">
-        <v>2.824214584393427</v>
+        <v>0.458934869963932</v>
       </c>
       <c r="E5" t="n">
-        <v>13.30578548438424</v>
+        <v>2.16219014121244</v>
       </c>
       <c r="F5" t="n">
-        <v>12.50933283402449</v>
+        <v>2.032766585528979</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.94322890591185</v>
+        <v>3.240774697210676</v>
       </c>
       <c r="D6" t="n">
-        <v>18.90671808960158</v>
+        <v>3.072341689560257</v>
       </c>
       <c r="E6" t="n">
-        <v>13.30578548438424</v>
+        <v>2.16219014121244</v>
       </c>
       <c r="F6" t="n">
-        <v>12.50933283402449</v>
+        <v>2.032766585528979</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.42681941518012</v>
+        <v>3.156858154966769</v>
       </c>
       <c r="D7" t="n">
-        <v>17.72085599583706</v>
+        <v>2.879639099323521</v>
       </c>
       <c r="E7" t="n">
-        <v>13.30578548438424</v>
+        <v>2.16219014121244</v>
       </c>
       <c r="F7" t="n">
-        <v>12.50933283402449</v>
+        <v>2.032766585528979</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.24999733528089</v>
+        <v>6.053124566983144</v>
       </c>
       <c r="D8" t="n">
-        <v>35.20228244364837</v>
+        <v>5.72037089709286</v>
       </c>
       <c r="E8" t="n">
-        <v>13.30578548438424</v>
+        <v>2.16219014121244</v>
       </c>
       <c r="F8" t="n">
-        <v>12.50933283402449</v>
+        <v>2.032766585528979</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.70601059228613</v>
+        <v>7.752226721246497</v>
       </c>
       <c r="D9" t="n">
-        <v>45.14135864784928</v>
+        <v>7.335470780275508</v>
       </c>
       <c r="E9" t="n">
-        <v>13.30578548438424</v>
+        <v>2.16219014121244</v>
       </c>
       <c r="F9" t="n">
-        <v>12.50933283402449</v>
+        <v>2.032766585528979</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
